--- a/Excel/jamesnocode.xlsx
+++ b/Excel/jamesnocode.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11560</v>
+        <v>34935</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -493,28 +493,88 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>LSH-EHgBvuo</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>OpenCode Crash Course: Build With AI Agents The Right Way</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>10787</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1:07:04</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>v0qPdxvWGxU</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Build a REAL Personal Finance App with OpenCode + Supabase (Full Beginner to Advanced Tutorial</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>2026-06-05</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>4327</v>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="D4" t="n">
+        <v>7466</v>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>1:24:13</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DwikL8QBcDU</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Codex vs. OpenCode (2026): The Truth After Real Testing</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2271</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0:36:45</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>N</t>
         </is>
